--- a/per-stock/CAMT/financials.xlsx
+++ b/per-stock/CAMT/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7845863936</v>
+        <v>8986040320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7569137664</v>
+        <v>8803590144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>171.78572</v>
+        <v>199.14285</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.205822</v>
+        <v>43.130905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15.720244</v>
+        <v>18.004742</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -717,7 +726,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>yfinance info.freeCashflow (FALLBACK levered estimate — statement TTM unavailable)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46604477</v>
+        <v>46044477</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>168.35</v>
+        <v>195.16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,471 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D49</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C49</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B49</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B36:E36)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D47</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C47</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B47</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B34:E34)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B30:E30)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1804,7 +2278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1829,27 +2303,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
         </is>
       </c>
     </row>
@@ -1882,19 +2356,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.106452</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.09912899999999999</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.149934</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.087252</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.100228</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.119173</v>
       </c>
     </row>
     <row r="4">
@@ -1904,19 +2378,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>27266000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-42528000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>31845000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>42896000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>32700000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>55563000</v>
       </c>
     </row>
     <row r="5">
@@ -1926,19 +2400,19 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="6">
@@ -1948,19 +2422,19 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>60730000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>64024000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>62951000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>60706000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>58074000</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>59161000</v>
       </c>
     </row>
     <row r="7">
@@ -1970,19 +2444,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>27266000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-42528000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>31845000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>42896000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>32700000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>55563000</v>
       </c>
     </row>
     <row r="8">
@@ -1992,19 +2466,19 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>27266000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>-42528000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>31845000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>42896000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>32700000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>55563000</v>
       </c>
     </row>
     <row r="9">
@@ -2014,19 +2488,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>8149000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>8163000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>6526000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>4942000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>5433000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>6138000</v>
       </c>
     </row>
     <row r="10">
@@ -2036,19 +2510,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8149000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>12136000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>6526000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>7308000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>5433000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>7847000</v>
       </c>
     </row>
     <row r="11">
@@ -2058,19 +2532,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="12">
@@ -2080,19 +2554,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="13">
@@ -2102,19 +2576,19 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>94393000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>96440000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>94148000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>91343000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>85938000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>85993000</v>
       </c>
     </row>
     <row r="14">
@@ -2124,19 +2598,19 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>27266000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>31684000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>31845000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>31974000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>32700000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>31300000</v>
       </c>
     </row>
     <row r="15">
@@ -2146,19 +2620,19 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>51471000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>51337000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>45755000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>49327000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>49286000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>49503000</v>
       </c>
     </row>
     <row r="16">
@@ -2168,19 +2642,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>46348000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>45814000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>45755000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>45682000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>45561000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>45428000</v>
       </c>
     </row>
     <row r="17">
@@ -2190,19 +2664,19 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>0.71</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-1.16</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>0.67</v>
       </c>
     </row>
     <row r="18">
@@ -2212,19 +2686,19 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>0.78</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-1.16</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.74</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>0.75</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.73</v>
       </c>
     </row>
     <row r="19">
@@ -2234,19 +2708,19 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>37394000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>34103000</v>
       </c>
     </row>
     <row r="20">
@@ -2256,19 +2730,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="21">
@@ -2278,19 +2752,19 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="22">
@@ -2300,19 +2774,19 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="23">
@@ -2322,19 +2796,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>31645000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>35897000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-53181000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>33695000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>34311000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>33009000</v>
       </c>
     </row>
     <row r="24">
@@ -2344,19 +2818,19 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>3770000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>3950000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-9380000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>3221000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>3822000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>4466000</v>
       </c>
     </row>
     <row r="25">
@@ -2366,19 +2840,19 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>35415000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>39847000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-62561000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>36916000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>38133000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>37475000</v>
       </c>
     </row>
     <row r="26">
@@ -2387,13 +2861,13 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-100932000</v>
       </c>
-      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
     </row>
@@ -2403,13 +2877,13 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-100932000</v>
       </c>
-      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
     </row>
@@ -2420,19 +2894,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>8149000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>8163000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>6526000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>4942000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>5433000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>6138000</v>
       </c>
     </row>
     <row r="29">
@@ -2442,19 +2916,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>8149000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>12136000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>6526000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>7308000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>5433000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>7847000</v>
       </c>
     </row>
     <row r="30">
@@ -2464,19 +2938,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>27266000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>31684000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>31845000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>31974000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>32700000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>31300000</v>
       </c>
     </row>
     <row r="31">
@@ -2486,19 +2960,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>33663000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>32416000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>31197000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>30637000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>27864000</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>26832000</v>
       </c>
     </row>
     <row r="32">
@@ -2508,19 +2982,19 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>14323000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>13056000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>13453000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>11474000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>10362000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>10371000</v>
       </c>
     </row>
     <row r="33">
@@ -2530,19 +3004,19 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>19340000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>19360000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>17744000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>19163000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>17502000</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>16461000</v>
       </c>
     </row>
     <row r="34">
@@ -2552,19 +3026,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>60929000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>64100000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>63042000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>62611000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>60564000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>58132000</v>
       </c>
     </row>
     <row r="35">
@@ -2574,19 +3048,19 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>60730000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>64024000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>62951000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>60706000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>58074000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>59161000</v>
       </c>
     </row>
     <row r="36">
@@ -2596,19 +3070,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>121659000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>128124000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>125993000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>123317000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>118638000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>117293000</v>
       </c>
     </row>
     <row r="37">
@@ -2618,19 +3092,19 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>121659000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>128124000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>125993000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>123317000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>118638000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>117293000</v>
       </c>
     </row>
   </sheetData>
@@ -2638,7 +3112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4324,7 +4798,1845 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>2092376</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2092376</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>2092376</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2092376</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>2092376</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>46044477</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>45828133</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>45766257</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>45702445</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>45603206</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>48136853</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>47920509</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>47858633</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>47794821</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>47695582</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>288214000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>341985000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>319440000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>6444000</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n">
+        <v>71701000</v>
+      </c>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>487811000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>530793000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>519111000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>200684000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>198198000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>598809000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>532596000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>492955000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>540483000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>501110000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1170339000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1136836000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1097147000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>824956000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>786120000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>825215000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>789570000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>781130000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>572963000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>546261000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>598809000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>532596000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>492955000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>540483000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>501110000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n">
+        <v>10960000</v>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n">
+        <v>9149000</v>
+      </c>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>682528000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>617003000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>578036000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>626484000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>587922000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1170339000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1136836000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1097147000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>824956000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>786120000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>682528000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>617003000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>578036000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>626484000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>587922000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>682528000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>617003000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>578036000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>626484000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>587922000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-1678000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>287000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>795000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-1678000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>287000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1520000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>795000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1898000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1898000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1898000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1898000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1898000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>418189000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>386544000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>350647000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>403828000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>370133000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>267735000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>231892000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>227589000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>223206000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>218715000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>177000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>178000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>177000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>615532000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>642830000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>653026000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>348257000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>346099000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>503263000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>535405000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>534331000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>218282000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>218367000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>14633000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>15220000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>15034000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n">
+        <v>10911000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n">
+        <v>1401000</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
+        <v>1840000</v>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n">
+        <v>1401000</v>
+      </c>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>819000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4892000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>5210000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>5135000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>3631000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>7304000</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>819000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1261000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5210000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5135000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>487811000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>528673000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>519111000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>198472000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>198198000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>8840000</v>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
+        <v>6661000</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>487811000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>519833000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>519111000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>198472000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>198198000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>112269000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>107425000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>118695000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>129975000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>127732000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>77964000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>13732000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>85463000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>13351000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>79598000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="n">
+        <v>17999000</v>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n">
+        <v>37621000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n">
+        <v>28919000</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="n">
+        <v>17999000</v>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n">
+        <v>37621000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n">
+        <v>28919000</v>
+      </c>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n"/>
+      <c r="C38" s="3" t="n">
+        <v>2120000</v>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n">
+        <v>2488000</v>
+      </c>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n">
+        <v>2120000</v>
+      </c>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n">
+        <v>2212000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>2488000</v>
+      </c>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n"/>
+      <c r="C40" s="3" t="n">
+        <v>19364000</v>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
+        <v>14902000</v>
+      </c>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>15708000</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>34305000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>54210000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>33232000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>61889000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>48134000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>8093000</v>
+      </c>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n">
+        <v>9890000</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n">
+        <v>7360000</v>
+      </c>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>34305000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>46117000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>33232000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>51999000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>48134000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n"/>
+      <c r="C44" s="3" t="n">
+        <v>12441000</v>
+      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n">
+        <v>11104000</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n">
+        <v>10072000</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n">
+        <v>12441000</v>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n">
+        <v>11104000</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>10072000</v>
+      </c>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>34305000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>33676000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>33232000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>40895000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>48134000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>1298060000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1259833000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1231062000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>974741000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>934021000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>360576000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>362838000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>331237000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>271803000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>260028000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>18336000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>17450000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>18624000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>17419000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>13999000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>12933000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>12933000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>10858000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3711000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>3090000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>12933000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>12933000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>10858000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>3711000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>3090000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>179488000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>182941000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>154460000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>107867000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>101101000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>179488000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>182941000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>154460000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>107867000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>101101000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>179488000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>182941000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>154460000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>107867000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>101101000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>83719000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>84407000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>85081000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>86001000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>86812000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>9374000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10062000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>10736000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>11656000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>12467000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>74345000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>74345000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>74345000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>74345000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>74345000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>66100000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>65107000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>62214000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>56805000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>55026000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>-35668000</v>
+      </c>
+      <c r="D59" s="3" t="n"/>
+      <c r="E59" s="3" t="n">
+        <v>-31717000</v>
+      </c>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>-25734000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>66100000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>100775000</v>
+      </c>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n">
+        <v>88522000</v>
+      </c>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n">
+        <v>79930000</v>
+      </c>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n"/>
+      <c r="C61" s="3" t="n">
+        <v>4737000</v>
+      </c>
+      <c r="D61" s="3" t="n"/>
+      <c r="E61" s="3" t="n">
+        <v>3769000</v>
+      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n">
+        <v>3508000</v>
+      </c>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>66100000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>10115000</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n">
+        <v>8462000</v>
+      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>9346000</v>
+      </c>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n"/>
+      <c r="C63" s="3" t="n">
+        <v>54964000</v>
+      </c>
+      <c r="D63" s="3" t="n"/>
+      <c r="E63" s="3" t="n">
+        <v>48882000</v>
+      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n">
+        <v>42231000</v>
+      </c>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n">
+        <v>29543000</v>
+      </c>
+      <c r="D64" s="3" t="n"/>
+      <c r="E64" s="3" t="n">
+        <v>25993000</v>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="3" t="n">
+        <v>23444000</v>
+      </c>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n"/>
+      <c r="C65" s="3" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="D65" s="3" t="n"/>
+      <c r="E65" s="3" t="n">
+        <v>1416000</v>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="3" t="n">
+        <v>1401000</v>
+      </c>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n"/>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>937484000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>896995000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>899825000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>702938000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>673993000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>35505000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>990000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>21337000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1494000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>22874000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>3409000</v>
+      </c>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n">
+        <v>3955000</v>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>5499000</v>
+      </c>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>99975000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>112202000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>126492000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>133709000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>129177000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n"/>
+      <c r="C71" s="3" t="n"/>
+      <c r="D71" s="3" t="n"/>
+      <c r="E71" s="3" t="n"/>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="3" t="n">
+        <v>35793000</v>
+      </c>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
+      <c r="C72" s="3" t="n"/>
+      <c r="D72" s="3" t="n"/>
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n">
+        <v>21445000</v>
+      </c>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n">
+        <v>53966000</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>131743000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>112234000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>112502000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>127787000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>100402000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n"/>
+      <c r="C75" s="3" t="n">
+        <v>11677000</v>
+      </c>
+      <c r="D75" s="3" t="n"/>
+      <c r="E75" s="3" t="n">
+        <v>7372000</v>
+      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="3" t="n">
+        <v>5457000</v>
+      </c>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Accrued Interest Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n"/>
+      <c r="C76" s="3" t="n">
+        <v>9728000</v>
+      </c>
+      <c r="D76" s="3" t="n"/>
+      <c r="E76" s="3" t="n">
+        <v>8397000</v>
+      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n">
+        <v>9269000</v>
+      </c>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>131743000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>90829000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>112502000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>112018000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>100402000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>670261000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>668160000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>639494000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>435993000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>421540000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>470664000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>490312000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>439823000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>243965000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>191745000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>199597000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>177848000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>199671000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>192028000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>229795000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5526,7 +7838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5547,7 +7859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
